--- a/data.xlsx
+++ b/data.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34474A24-3E11-448C-A92C-51DAB7C0C26A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Настройки" sheetId="1" r:id="rId1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dluki\Downloads\Online preza gdk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34474A24-3E11-448C-A92C-51DAB7C0C26A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F4E136D-AB48-4C16-896E-752BCF01C26C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Настройки" sheetId="1" r:id="rId1"/>
@@ -96,9 +96,6 @@
     <t>event_text</t>
   </si>
   <si>
-    <t>Начало бетонирования фундаментов под ОФ. Общая строительная готовность составляет 9,4% (+0,6%). Общая сумма оплат составила 28,4 млрд руб. с НДС (+1,2 млрд руб.).</t>
-  </si>
-  <si>
     <t>Текст ключевого события (раздел «Показатели»)</t>
   </si>
   <si>
@@ -940,6 +937,9 @@
   </si>
   <si>
     <t>Площадка</t>
+  </si>
+  <si>
+    <t>Начало бетонирования фундаментов под ОФ. Общая строительная готовность составляет  19,4% (+0,6%). Общая сумма оплат составила 28,4 млрд руб. с НДС (+1,2 млрд руб.).</t>
   </si>
 </sst>
 </file>
@@ -1476,7 +1476,7 @@
         <v>16</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>17</v>
@@ -1498,54 +1498,54 @@
         <v>21</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11" s="3">
         <v>19.600000000000001</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B13" s="3">
         <v>18.600000000000001</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1570,7 +1570,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1585,119 +1585,119 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H7" s="3"/>
     </row>
@@ -1720,7 +1720,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1733,132 +1733,132 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="E5" s="3">
         <v>99.7</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3">
         <v>54.3</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="E9" s="3">
         <v>19.399999999999999</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -1880,70 +1880,70 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B2" s="3">
         <v>73</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B3" s="3">
         <v>35</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B4" s="3">
         <v>27</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1962,7 +1962,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1974,221 +1974,221 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>258</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>262</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>266</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>270</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>274</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>278</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>282</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>286</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B12" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>289</v>
-      </c>
       <c r="D12" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="D13" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="E13" s="6" t="s">
         <v>292</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="22.8">
       <c r="A14" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
       <c r="D14" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E14" s="7"/>
     </row>
     <row r="15" spans="1:5" ht="22.8">
       <c r="A15" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
       <c r="D15" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E15" s="9"/>
     </row>
     <row r="16" spans="1:5" ht="22.8">
       <c r="A16" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
       <c r="D16" s="12" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E16" s="11"/>
     </row>
@@ -2215,7 +2215,7 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -2234,48 +2234,48 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>130</v>
-      </c>
       <c r="L3" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="C4" s="3">
         <v>1.6</v>
@@ -2287,16 +2287,16 @@
         <v>0.6</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>134</v>
       </c>
       <c r="H4" s="3">
         <v>34</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J4" s="3">
         <v>848</v>
@@ -2305,15 +2305,15 @@
         <v>451</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="C5" s="3">
         <v>0</v>
@@ -2325,16 +2325,16 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="H5" s="3">
         <v>12.1</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J5" s="3">
         <v>947</v>
@@ -2343,15 +2343,15 @@
         <v>636</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>142</v>
       </c>
       <c r="C6" s="3">
         <v>12</v>
@@ -2363,16 +2363,16 @@
         <v>2</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H6" s="3">
         <v>7</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J6" s="3">
         <v>505</v>
@@ -2381,15 +2381,15 @@
         <v>425</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="C7" s="3">
         <v>9</v>
@@ -2401,16 +2401,16 @@
         <v>1.5</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H7" s="3">
         <v>5</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J7" s="3">
         <v>402</v>
@@ -2419,15 +2419,15 @@
         <v>246</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="C8" s="3">
         <v>82</v>
@@ -2439,16 +2439,16 @@
         <v>4</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>152</v>
       </c>
       <c r="H8" s="3">
         <v>6.9</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J8" s="3">
         <v>932</v>
@@ -2457,15 +2457,15 @@
         <v>330</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C9" s="3">
         <v>31</v>
@@ -2477,16 +2477,16 @@
         <v>3</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H9" s="3">
         <v>2.5</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J9" s="3">
         <v>690</v>
@@ -2495,15 +2495,15 @@
         <v>447</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C10" s="3">
         <v>86</v>
@@ -2515,16 +2515,16 @@
         <v>2.1</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H10" s="3">
         <v>0.8</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J10" s="3">
         <v>905</v>
@@ -2533,15 +2533,15 @@
         <v>548</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C11" s="3">
         <v>100</v>
@@ -2553,16 +2553,16 @@
         <v>0</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H11" s="3">
         <v>0.7</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J11" s="3">
         <v>700</v>
@@ -2571,15 +2571,15 @@
         <v>560</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="C12" s="3">
         <v>18</v>
@@ -2591,16 +2591,16 @@
         <v>2</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H12" s="3">
         <v>3</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J12" s="3">
         <v>752</v>
@@ -2609,15 +2609,15 @@
         <v>400</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>165</v>
       </c>
       <c r="C13" s="3">
         <v>24</v>
@@ -2629,16 +2629,16 @@
         <v>3</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H13" s="3">
         <v>4</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J13" s="3">
         <v>686</v>
@@ -2647,15 +2647,15 @@
         <v>290</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>168</v>
       </c>
       <c r="C14" s="3">
         <v>46</v>
@@ -2667,16 +2667,16 @@
         <v>4</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H14" s="3">
         <v>6</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J14" s="3">
         <v>690</v>
@@ -2685,15 +2685,15 @@
         <v>172</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="C15" s="3">
         <v>38</v>
@@ -2705,16 +2705,16 @@
         <v>3.5</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H15" s="3">
         <v>5</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J15" s="3">
         <v>430</v>
@@ -2723,15 +2723,15 @@
         <v>545</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>175</v>
       </c>
       <c r="C16" s="3">
         <v>100</v>
@@ -2743,16 +2743,16 @@
         <v>8</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H16" s="3">
         <v>3</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J16" s="3">
         <v>511</v>
@@ -2761,15 +2761,15 @@
         <v>587</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>178</v>
       </c>
       <c r="C17" s="3">
         <v>0</v>
@@ -2781,16 +2781,16 @@
         <v>0</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H17" s="3">
         <v>3</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J17" s="3">
         <v>708</v>
@@ -2799,15 +2799,15 @@
         <v>636</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>180</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>181</v>
       </c>
       <c r="C18" s="3">
         <v>0</v>
@@ -2819,16 +2819,16 @@
         <v>0</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H18" s="3">
         <v>4</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J18" s="3">
         <v>941</v>
@@ -2837,15 +2837,15 @@
         <v>578</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="C19" s="3">
         <v>58</v>
@@ -2857,16 +2857,16 @@
         <v>5</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H19" s="3">
         <v>3</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J19" s="3">
         <v>812</v>
@@ -2875,7 +2875,7 @@
         <v>200</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -2898,7 +2898,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -2912,40 +2912,40 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="D3" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>188</v>
       </c>
       <c r="C4" s="3">
         <v>7.5</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F4" s="3">
         <v>296</v>
@@ -2956,19 +2956,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>191</v>
       </c>
       <c r="C5" s="3">
         <v>32</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>192</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>193</v>
       </c>
       <c r="F5" s="3">
         <v>406</v>
@@ -2979,17 +2979,17 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>194</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>195</v>
       </c>
       <c r="C6" s="3">
         <v>1</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F6" s="3">
         <v>511</v>
@@ -3000,19 +3000,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>197</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>198</v>
       </c>
       <c r="C7" s="3">
         <v>39</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>200</v>
       </c>
       <c r="F7" s="3">
         <v>612</v>
@@ -3023,17 +3023,17 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>202</v>
       </c>
       <c r="C8" s="3">
         <v>0</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F8" s="3">
         <v>708</v>
@@ -3044,17 +3044,17 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>205</v>
       </c>
       <c r="C9" s="3">
         <v>0</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F9" s="3">
         <v>380</v>
@@ -3065,17 +3065,17 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>208</v>
       </c>
       <c r="C10" s="3">
         <v>14</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F10" s="3">
         <v>732</v>
@@ -3086,19 +3086,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>211</v>
       </c>
       <c r="C11" s="3">
         <v>0</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>213</v>
       </c>
       <c r="F11" s="3">
         <v>178</v>
@@ -3109,17 +3109,17 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>214</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>215</v>
       </c>
       <c r="C12" s="3">
         <v>9.8000000000000007</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F12" s="3">
         <v>214</v>
@@ -3130,17 +3130,17 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>217</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>218</v>
       </c>
       <c r="C13" s="3">
         <v>99.9</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F13" s="3">
         <v>52</v>
@@ -3165,7 +3165,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -3179,92 +3179,92 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>226</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>302</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>303</v>
       </c>
       <c r="G4" s="3"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>233</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>238</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -3283,7 +3283,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3293,13 +3293,13 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>242</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3307,7 +3307,7 @@
         <v>2025</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -3316,7 +3316,7 @@
         <v>2026</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C5" s="3"/>
     </row>
@@ -3325,10 +3325,10 @@
         <v>2026</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3336,7 +3336,7 @@
         <v>2026</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C7" s="3"/>
     </row>
@@ -3345,7 +3345,7 @@
         <v>2026</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C8" s="3"/>
     </row>
@@ -3354,7 +3354,7 @@
         <v>2027</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C9" s="3"/>
     </row>
@@ -3363,7 +3363,7 @@
         <v>2027</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C10" s="3"/>
     </row>
@@ -3372,7 +3372,7 @@
         <v>2027</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C11" s="3"/>
     </row>
@@ -3381,7 +3381,7 @@
         <v>2027</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C12" s="3"/>
     </row>
@@ -3390,7 +3390,7 @@
         <v>2028</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C13" s="3"/>
     </row>
@@ -3399,7 +3399,7 @@
         <v>2028</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C14" s="3"/>
     </row>
@@ -3408,7 +3408,7 @@
         <v>2028</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C15" s="3"/>
     </row>
@@ -3417,7 +3417,7 @@
         <v>2028</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C16" s="3"/>
     </row>
